--- a/スクリーンショット_使い方_エネミー.xlsx
+++ b/スクリーンショット_使い方_エネミー.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1807dd80cee582b/ドキュメント/TRPG/01_ログ・ホライズン/ccfolia_駒作成/web_App/lhtrpg_webapp_challenge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K.Housako\dev\lhtrpg_webapp_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92F9F78D-BF30-411F-BBBE-5495AA8A73B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442DD976-99CE-4446-9D4D-077C0138EABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="1065" windowWidth="11445" windowHeight="10260" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
+    <workbookView xWindow="6675" yWindow="3945" windowWidth="21585" windowHeight="11295" activeTab="2" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -102,16 +103,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>207818</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>535736</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>95618</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>138545</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>69272</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -126,10 +127,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="266700" y="329565"/>
-          <a:ext cx="12937286" cy="19764743"/>
-          <a:chOff x="2258546" y="491602"/>
-          <a:chExt cx="13586891" cy="20239089"/>
+          <a:off x="1333500" y="1065068"/>
+          <a:ext cx="10806545" cy="22435704"/>
+          <a:chOff x="3397701" y="1040241"/>
+          <a:chExt cx="11335848" cy="19124022"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -145,10 +146,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="2258546" y="491602"/>
-            <a:ext cx="13586891" cy="20239089"/>
-            <a:chOff x="-855407" y="-7728154"/>
-            <a:chExt cx="13303046" cy="19762839"/>
+            <a:off x="3397701" y="1040241"/>
+            <a:ext cx="11335848" cy="19124022"/>
+            <a:chOff x="259951" y="-7192425"/>
+            <a:chExt cx="11099029" cy="18674011"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -164,15 +165,13 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="-855407" y="-7728154"/>
-              <a:ext cx="13303046" cy="19762839"/>
+              <a:off x="259951" y="-7192425"/>
+              <a:ext cx="11099029" cy="18674011"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
+            <a:ln/>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
@@ -304,16 +303,17 @@
               <a:picLocks noChangeAspect="1"/>
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
-          <xdr:blipFill>
+          <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="3511" r="6080"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1218340" y="4701892"/>
-              <a:ext cx="9515475" cy="6715125"/>
+              <a:off x="1552370" y="4701892"/>
+              <a:ext cx="8602795" cy="6715125"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -333,17 +333,17 @@
               <a:picLocks noChangeAspect="1"/>
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
-          <xdr:blipFill>
+          <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:srcRect b="5882"/>
+            <a:srcRect l="15627" r="14777" b="5882"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="-515275" y="-1302363"/>
-              <a:ext cx="12744000" cy="6651603"/>
+              <a:off x="1476238" y="-1302363"/>
+              <a:ext cx="8869255" cy="6651603"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -363,16 +363,17 @@
               <a:picLocks noChangeAspect="1"/>
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
-          <xdr:blipFill>
+          <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:srcRect l="9123" r="14411"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="407198" y="-7149646"/>
-              <a:ext cx="11300400" cy="7965543"/>
+              <a:off x="1438172" y="-7149646"/>
+              <a:ext cx="8640862" cy="7965543"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1329,14 +1330,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>34291</xdr:rowOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>51608</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>269037</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>209552</xdr:rowOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>226869</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -1351,8 +1352,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1" y="20751166"/>
-          <a:ext cx="12937286" cy="4933951"/>
+          <a:off x="1" y="41771108"/>
+          <a:ext cx="12937286" cy="5890261"/>
           <a:chOff x="2260630" y="491603"/>
           <a:chExt cx="13585449" cy="5061742"/>
         </a:xfrm>
@@ -1531,15 +1532,15 @@
           </xdr:nvPicPr>
           <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:srcRect b="54579"/>
+            <a:srcRect l="9638" r="13258" b="54579"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="407198" y="-7149645"/>
-              <a:ext cx="11300400" cy="3618128"/>
+              <a:off x="1496396" y="-7149645"/>
+              <a:ext cx="8712993" cy="3618128"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2000,15 +2001,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>675929</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:colOff>604492</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>55419</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>288951</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>156211</xdr:rowOff>
+      <xdr:colOff>217514</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>173529</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2023,8 +2024,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13999499" y="17659351"/>
-          <a:ext cx="12955642" cy="7501890"/>
+          <a:off x="13939492" y="35202669"/>
+          <a:ext cx="12948022" cy="8976360"/>
           <a:chOff x="2258546" y="491603"/>
           <a:chExt cx="13586891" cy="7664485"/>
         </a:xfrm>
@@ -2203,15 +2204,15 @@
           </xdr:nvPicPr>
           <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:srcRect t="-1" b="17022"/>
+            <a:srcRect l="10035" t="-1" r="13670" b="19919"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="407198" y="-7149645"/>
-              <a:ext cx="11300400" cy="6609714"/>
+              <a:off x="1541143" y="-7149644"/>
+              <a:ext cx="8621738" cy="6378972"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2391,14 +2392,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>152409</xdr:rowOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>169726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>270941</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>222883</xdr:rowOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>240200</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2413,8 +2414,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="26108034"/>
-          <a:ext cx="12941096" cy="7450444"/>
+          <a:off x="0" y="48175726"/>
+          <a:ext cx="12939191" cy="8928724"/>
           <a:chOff x="2258546" y="6676941"/>
           <a:chExt cx="13586891" cy="7615458"/>
         </a:xfrm>
@@ -2591,17 +2592,17 @@
               <a:picLocks noChangeAspect="1"/>
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
-          <xdr:blipFill>
+          <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:srcRect b="5882"/>
+            <a:srcRect l="16307" r="16807" b="10033"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="-515275" y="-1302475"/>
-              <a:ext cx="12744000" cy="6649842"/>
+              <a:off x="1562877" y="-1302475"/>
+              <a:ext cx="8524021" cy="6356600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2781,14 +2782,14 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>670560</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>141142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>251891</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>24764</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>42082</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2803,8 +2804,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14001750" y="25843229"/>
-          <a:ext cx="12916331" cy="6800850"/>
+          <a:off x="14005560" y="47861392"/>
+          <a:ext cx="12916331" cy="8187690"/>
           <a:chOff x="2258546" y="13132769"/>
           <a:chExt cx="13586891" cy="6977784"/>
         </a:xfrm>
@@ -2981,16 +2982,17 @@
               <a:picLocks noChangeAspect="1"/>
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
-          <xdr:blipFill>
+          <xdr:blipFill rotWithShape="1">
             <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="2944" r="6414"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1218340" y="4701892"/>
-              <a:ext cx="9515475" cy="6715125"/>
+              <a:off x="1498529" y="4701892"/>
+              <a:ext cx="8624926" cy="6715125"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3137,6 +3139,4937 @@
           <a:xfrm flipH="1">
             <a:off x="13232648" y="16418503"/>
             <a:ext cx="274619" cy="246697"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>432953</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>17321</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="22" name="グループ化 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D8C0DA1-0E9C-4007-ADCB-83320746D7F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="14434703" y="995795"/>
+          <a:ext cx="10919118" cy="22435704"/>
+          <a:chOff x="3327725" y="1040241"/>
+          <a:chExt cx="11475801" cy="19124022"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="23" name="グループ化 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{448129B0-571D-6EBF-1F81-9E28D018B4A2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3327725" y="1040241"/>
+            <a:ext cx="11475801" cy="19124022"/>
+            <a:chOff x="191437" y="-7192425"/>
+            <a:chExt cx="11236058" cy="18674011"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="50" name="正方形/長方形 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5889C73-9604-CBA7-0C69-670631356A5D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="191437" y="-7192425"/>
+              <a:ext cx="11236058" cy="18674011"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="51" name="図 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D0C66F1-81E2-0102-7863-F573C3438A5A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="3511" r="6080"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1552370" y="4701892"/>
+              <a:ext cx="8602795" cy="6715125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="52" name="図 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E994C48-DD1A-C400-E7D5-59118E8A5D95}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:srcRect l="15627" r="14777" b="5882"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1476238" y="-1302363"/>
+              <a:ext cx="8869255" cy="6651603"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="53" name="図 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D63A7A3-CBA8-067A-4C1A-B95198A416FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:srcRect l="9123" r="14411"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1438172" y="-7149646"/>
+              <a:ext cx="8640862" cy="7965543"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="29" name="正方形/長方形 28">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D937F43B-13B7-C71E-57C6-2959998BE0B8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4967720" y="3447877"/>
+            <a:ext cx="8272548" cy="3867323"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="32" name="正方形/長方形 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF2D37AD-5F9E-07C4-63D9-64E7ED1CE4A4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4975340" y="7472103"/>
+            <a:ext cx="8259213" cy="5818043"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="正方形/長方形 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A83652A-2984-B9C7-531D-1A10374CF2AE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4979150" y="13593215"/>
+            <a:ext cx="8253498" cy="6139468"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="34" name="直線矢印コネクタ 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94A0FDCC-1524-BA2F-FBE0-86035C28566E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:cxnSpLocks/>
+            <a:stCxn id="35" idx="2"/>
+            <a:endCxn id="55" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13451259" y="2256189"/>
+            <a:ext cx="587953" cy="283961"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="35" name="正方形/長方形 34">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7022E403-086A-5511-24B1-C31092EAECFC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13537301" y="1828082"/>
+            <a:ext cx="1003822" cy="428106"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>①基本操作</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="40" name="正方形/長方形 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BBB460E-0217-9447-0EBE-6F6C35E3EF08}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13519218" y="4823807"/>
+            <a:ext cx="1170410" cy="714548"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>②エネミー</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　情報入力欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="43" name="直線矢印コネクタ 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929E5C2C-1A3C-EE04-328E-ED0D5EC6E190}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="40" idx="1"/>
+            <a:endCxn id="29" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13238363" y="5187142"/>
+            <a:ext cx="278950" cy="198207"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="44" name="正方形/長方形 43">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF25F564-691C-8761-0036-0A75897C9509}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13507268" y="9795164"/>
+            <a:ext cx="1129367" cy="700000"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>③ドロップ</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　入力欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="45" name="直線矢印コネクタ 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEB79D9-5CDF-B5C6-5450-0FEB50019FEA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="44" idx="1"/>
+            <a:endCxn id="32" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13232648" y="10143866"/>
+            <a:ext cx="274620" cy="239164"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="46" name="正方形/長方形 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F683B288-D98A-0F16-5CDB-175C510779D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13507267" y="16002001"/>
+            <a:ext cx="1135083" cy="834908"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>④エネミー</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　能力値欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8C2CA9-70A7-8A26-1E96-46B1B1028803}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="46" idx="1"/>
+            <a:endCxn id="33" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13232648" y="16418503"/>
+            <a:ext cx="274619" cy="246697"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="55" name="正方形/長方形 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F10FEA9-393D-DF7A-50F4-942925534B91}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4756728" y="1721723"/>
+            <a:ext cx="8694531" cy="1636853"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>51027</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>578431</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>153079</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="38" name="グループ化 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE229200-2AD2-BD8E-1054-B47E1C8A1EE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12620625" y="19339152"/>
+          <a:ext cx="11436931" cy="4626427"/>
+          <a:chOff x="3327725" y="3056932"/>
+          <a:chExt cx="11475801" cy="4655945"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="39" name="グループ化 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ECF3CB1-ED0C-B0ED-6A59-C4776D570463}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3327725" y="3056932"/>
+            <a:ext cx="11475801" cy="4655945"/>
+            <a:chOff x="191437" y="-5223189"/>
+            <a:chExt cx="11236058" cy="4546385"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="52" name="正方形/長方形 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AE5EF6D-5F1D-D845-AB37-0967E92907A5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="191437" y="-5223189"/>
+              <a:ext cx="11236058" cy="4546385"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="55" name="図 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F9E84E0-0EF0-17FC-6FE4-B2FEC3957663}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="9123" t="27121" r="14411" b="20370"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1438172" y="-4989374"/>
+              <a:ext cx="8640862" cy="4182676"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="40" name="正方形/長方形 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B1F501-50A0-F874-0098-AE3005047196}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4967720" y="3447877"/>
+            <a:ext cx="8272548" cy="3867323"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="45" name="正方形/長方形 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB687877-C95E-F730-40C5-963B3E524E38}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13519218" y="5012001"/>
+            <a:ext cx="1170410" cy="714548"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>④エネミー</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　情報入力欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="46" name="直線矢印コネクタ 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A959EEC2-3229-4685-6297-95CB3BF1ED7C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="45" idx="1"/>
+            <a:endCxn id="40" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13240268" y="5369275"/>
+            <a:ext cx="278950" cy="12264"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>176294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>464131</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="56" name="グループ化 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCF63B2B-92DE-EEDE-BB23-9013603FA423}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="766763" y="24226919"/>
+          <a:ext cx="11436931" cy="6640884"/>
+          <a:chOff x="3327725" y="7144405"/>
+          <a:chExt cx="11475801" cy="6683747"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="57" name="グループ化 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EB51DEE-5808-291B-A3F7-AA7129F4668C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3327725" y="7144405"/>
+            <a:ext cx="11475801" cy="6683747"/>
+            <a:chOff x="191437" y="-1231899"/>
+            <a:chExt cx="11236058" cy="6526470"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="70" name="正方形/長方形 69">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{268A61E6-79E2-C9A3-C617-68920D6336D8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="191437" y="-1231899"/>
+              <a:ext cx="11236058" cy="6526470"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="72" name="図 71">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD9F062-85AA-D064-39D2-7F4ED39383FF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:srcRect l="15627" t="4316" r="14777" b="8679"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1476238" y="-997331"/>
+              <a:ext cx="8869255" cy="6148906"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="59" name="正方形/長方形 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D17EF6ED-BB5B-FEC0-0415-C8155E3DBC27}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4975340" y="7472103"/>
+            <a:ext cx="8259213" cy="5818043"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="65" name="正方形/長方形 64">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5184658-F8E9-16B2-DC94-C3C0AAB93B38}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13507268" y="10023325"/>
+            <a:ext cx="1129367" cy="700000"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>⑤ドロップ</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　入力欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="66" name="直線矢印コネクタ 65">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB0A87B0-B5D5-5B68-801A-EA26B1615E90}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="65" idx="1"/>
+            <a:endCxn id="59" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13234553" y="10373324"/>
+            <a:ext cx="272715" cy="7800"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>6931</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>146338</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="74" name="グループ化 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE73E18B-8A7D-D537-2958-C6396BAC1E16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12734925" y="24422100"/>
+          <a:ext cx="11441694" cy="6918613"/>
+          <a:chOff x="3327725" y="13208673"/>
+          <a:chExt cx="11475801" cy="6955591"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="75" name="グループ化 74">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41384F35-0CEF-B8ED-8F74-AEF6E8EBE08F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3327725" y="13208673"/>
+            <a:ext cx="11475801" cy="6955591"/>
+            <a:chOff x="191437" y="4689668"/>
+            <a:chExt cx="11236058" cy="6791917"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="88" name="正方形/長方形 87">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C72269-4EF7-F0CC-7BFB-53242E8D5D67}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="191437" y="4689668"/>
+              <a:ext cx="11236058" cy="6791917"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="89" name="図 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8592C5CD-58BC-A0AB-8E85-4B7D2D166A2A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:srcRect l="3511" r="6080"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1552370" y="4701892"/>
+              <a:ext cx="8602795" cy="6715125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="78" name="正方形/長方形 77">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33BB5E1E-97BD-B636-8509-AEC8088AB8B2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4979150" y="13593215"/>
+            <a:ext cx="8253498" cy="6139468"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="85" name="正方形/長方形 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75680283-7362-7DDE-1569-5744E23EB63D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13507267" y="16241399"/>
+            <a:ext cx="1135083" cy="834908"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent6"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent6"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>⑥エネミー</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>　能力値欄</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="86" name="直線矢印コネクタ 85">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBF7E58-18E7-2633-DC2A-8AD15D36AFF5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="85" idx="1"/>
+            <a:endCxn id="78" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13232648" y="16658853"/>
+            <a:ext cx="274619" cy="4097"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>433388</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>236085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>135520</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="53" name="グループ化 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EA19919-1A77-FDE5-A212-E4824B4AC7BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="433388" y="20000460"/>
+          <a:ext cx="11441695" cy="3502478"/>
+          <a:chOff x="552450" y="20730244"/>
+          <a:chExt cx="11322632" cy="3463257"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="21" name="グループ化 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8A50976-DBD1-58BA-52DB-BBE1BBEE8312}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="552450" y="20730244"/>
+            <a:ext cx="11322632" cy="3463257"/>
+            <a:chOff x="191437" y="-7192425"/>
+            <a:chExt cx="11236058" cy="3428276"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="34" name="正方形/長方形 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0378E38A-FB7E-E6CD-71C1-88C9B77D0837}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="191437" y="-7192425"/>
+              <a:ext cx="11236058" cy="3428276"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="37" name="図 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ED8D197-3A02-7ACA-1062-57CB0A8E6BC8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="9123" r="14411" b="65718"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1438172" y="-7149646"/>
+              <a:ext cx="8640862" cy="2730754"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="22" name="グループ化 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C78905AE-B080-46EB-9BBB-F6846C47D2DC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2004284" y="21413851"/>
+            <a:ext cx="8462009" cy="1585034"/>
+            <a:chOff x="4730115" y="1848880"/>
+            <a:chExt cx="8885958" cy="1362085"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="正方形/長方形 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CE4FF44-71B9-F0A8-10AA-89064D2EBBE3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="正方形/長方形 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1672D39-40EF-3846-811A-CBECB20ECF2C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2823384"/>
+              <a:ext cx="1301288" cy="364529"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="正方形/長方形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7923A77-A681-2AD2-2CE3-6E093596B195}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12286368" y="1878276"/>
+              <a:ext cx="1329705" cy="346668"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90C7D8DD-B64C-835B-A763-CBB4DA377207}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="30" idx="1"/>
+              <a:endCxn id="24" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="30" name="正方形/長方形 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{133EF851-6355-1137-0773-7D9DD7ACC252}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="正方形/長方形 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB15318-D6A8-A46D-11E5-0D27481EFD01}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6585238" y="2790480"/>
+              <a:ext cx="2157623" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②入力ファイルの読み込み</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="32" name="直線矢印コネクタ 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{555097AD-6C71-266B-BF9F-1D103842C238}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="31" idx="1"/>
+              <a:endCxn id="27" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="6247535" y="3000723"/>
+              <a:ext cx="337703" cy="4926"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="35" name="正方形/長方形 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71081778-A736-2BF6-8B21-95193F634ABE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10204354" y="1848880"/>
+              <a:ext cx="1640080" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③入力内容をクリア</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="36" name="直線矢印コネクタ 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D36933-6849-D599-4E14-BACE2D6995D8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="35" idx="3"/>
+              <a:endCxn id="28" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11844434" y="2049252"/>
+              <a:ext cx="441934" cy="2358"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>583194</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>213013</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="82" name="グループ化 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F64B540-BE8C-0B3F-0C77-B712161BC309}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="190500" y="0"/>
+          <a:ext cx="11441694" cy="19024888"/>
+          <a:chOff x="495300" y="314325"/>
+          <a:chExt cx="11441694" cy="19024888"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="2" name="グループ化 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4313106B-5620-4C72-B153-1A5F31039641}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="495300" y="314325"/>
+            <a:ext cx="11441694" cy="19024888"/>
+            <a:chOff x="3327725" y="1040241"/>
+            <a:chExt cx="11475801" cy="19124022"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="3" name="グループ化 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BAB3D4A-8172-A04B-F527-58319D4ABE0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="3327725" y="1040241"/>
+              <a:ext cx="11475801" cy="19124022"/>
+              <a:chOff x="191437" y="-7192425"/>
+              <a:chExt cx="11236058" cy="18674011"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="16" name="正方形/長方形 15">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0622D09D-C287-AC17-5FBF-C440DD5BF06B}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="191437" y="-7192425"/>
+                <a:ext cx="11236058" cy="18674011"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="dk1"/>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="lt1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="dk1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+              <a:lstStyle>
+                <a:defPPr>
+                  <a:defRPr lang="ja-JP"/>
+                </a:defPPr>
+                <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl1pPr>
+                <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl2pPr>
+                <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl3pPr>
+                <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl4pPr>
+                <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl5pPr>
+                <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl6pPr>
+                <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl7pPr>
+                <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl8pPr>
+                <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                  <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:lvl9pPr>
+              </a:lstStyle>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="17" name="図 16">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{473DDA88-E27C-4A57-F196-D5472179BFA5}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+              <a:srcRect l="3511" r="6080"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1552370" y="4701892"/>
+                <a:ext cx="8602795" cy="6715125"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="18" name="図 17">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45AF5E9B-03D6-4AB1-1676-F897EC1E4B66}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+              <a:srcRect l="15627" r="14777" b="5882"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1476238" y="-1302363"/>
+                <a:ext cx="8869255" cy="6651603"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="19" name="図 18">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724E5798-6B4D-8335-294F-FFE337B9910E}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+              <a:srcRect l="9123" r="14411"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="1438172" y="-7149646"/>
+                <a:ext cx="8640862" cy="7965543"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="正方形/長方形 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FF1069A-A88D-ECCA-B2D3-D5E5EA42DE82}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4967720" y="3447877"/>
+              <a:ext cx="8272548" cy="3867323"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="正方形/長方形 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0E6D1CA-FE3F-BD19-107E-ECC42C57A33E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4975340" y="7472103"/>
+              <a:ext cx="8259213" cy="5818043"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="正方形/長方形 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A06FF8C-BBF1-A37D-99A5-8EC634E1711A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4979150" y="13593215"/>
+              <a:ext cx="8253498" cy="6139468"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="正方形/長方形 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68340B4-6D24-E1D2-B115-6F171BA29353}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13519218" y="4823807"/>
+              <a:ext cx="1170410" cy="714548"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④エネミー</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>　情報入力欄</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CDDD4D-0B14-0752-6CA5-ED2B32D28DB7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="9" idx="1"/>
+              <a:endCxn id="4" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="13238363" y="5187142"/>
+              <a:ext cx="278950" cy="198207"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F70571-B6B2-13D4-D227-24B29505C168}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13507268" y="9795164"/>
+              <a:ext cx="1129367" cy="700000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑤ドロップ</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>　入力欄</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50B8946C-E226-2A43-27FE-92A7329BAA3A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="11" idx="1"/>
+              <a:endCxn id="5" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="13232648" y="10143866"/>
+              <a:ext cx="274620" cy="239164"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="正方形/長方形 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32848968-827C-725D-E743-131CBFBB5A52}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13507267" y="16002001"/>
+              <a:ext cx="1135083" cy="834908"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑥エネミー</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>　能力値欄</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C83085F6-8CDA-B12B-DEC4-FF49022A0FDF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="13" idx="1"/>
+              <a:endCxn id="6" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="13232648" y="16418503"/>
+              <a:ext cx="274619" cy="246697"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="63" name="グループ化 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1F3D28A-2366-4058-B8C0-9AF10E9EAFFF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1962401" y="1005669"/>
+            <a:ext cx="8550991" cy="1602984"/>
+            <a:chOff x="4730115" y="1848880"/>
+            <a:chExt cx="8885958" cy="1362085"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="64" name="正方形/長方形 63">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1854A21-90D8-7B80-E985-12453F5DE690}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="67" name="正方形/長方形 66">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED802243-87DD-6226-8472-F7A2537619C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2823384"/>
+              <a:ext cx="1301288" cy="364529"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="68" name="正方形/長方形 67">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E8FFF4E-F31F-5793-E540-4AFFB749927D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12286368" y="1878276"/>
+              <a:ext cx="1329705" cy="346668"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="69" name="直線矢印コネクタ 68">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E4CC36-680F-CB3C-2850-AFE93141BF78}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="71" idx="1"/>
+              <a:endCxn id="64" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="71" name="正方形/長方形 70">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3CF621C-5E25-3F99-A481-0B0B64736FB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="73" name="正方形/長方形 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA0463E3-3F5C-394A-9326-56603CC5E8C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6585238" y="2790480"/>
+              <a:ext cx="2157623" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②入力ファイルの読み込み</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="76" name="直線矢印コネクタ 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2472F7D2-2107-3228-25FE-1A2F85169989}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="73" idx="1"/>
+              <a:endCxn id="67" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="6247535" y="3000723"/>
+              <a:ext cx="337703" cy="4926"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="77" name="正方形/長方形 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26F9E13D-A368-6634-3CA4-62E95FC0D867}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10204354" y="1848880"/>
+              <a:ext cx="1640080" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③入力内容をクリア</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="79" name="直線矢印コネクタ 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7DA71E8-81AA-3491-4CD7-E16D27753BA2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="77" idx="3"/>
+              <a:endCxn id="68" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11844434" y="2049252"/>
+              <a:ext cx="441934" cy="2358"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>71747</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>52517</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>89065</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="48" name="グループ化 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF095A9-DF45-22C9-52E4-5DBA06E8D74A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="176893" y="2031176"/>
+          <a:ext cx="11441695" cy="10794175"/>
+          <a:chOff x="2628901" y="2760518"/>
+          <a:chExt cx="11534223" cy="10075718"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="25" name="グループ化 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{679A62CA-420C-4938-2B65-6358357E4B59}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2628901" y="2760518"/>
+            <a:ext cx="11534223" cy="10075718"/>
+            <a:chOff x="2649683" y="2667000"/>
+            <a:chExt cx="11651986" cy="10685318"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="正方形/長方形 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82EFC521-04B3-A544-B2A4-7B412D68067E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2649683" y="2667000"/>
+              <a:ext cx="11651986" cy="10685318"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="ja-JP"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="図 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A6098B-0B2A-2166-4B8F-CC8676042F30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="7536" t="7445" r="9528"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4069772" y="3186545"/>
+              <a:ext cx="8866909" cy="5998667"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="図 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADA2147D-611B-5810-BAFD-F784A0D9A096}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:srcRect l="10152" t="33089" r="6017" b="8081"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4069773" y="8978313"/>
+              <a:ext cx="8866910" cy="4200823"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="13" name="グループ化 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6271005-8921-50A2-0D01-7789575A2374}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="4109112" y="3636981"/>
+            <a:ext cx="8460424" cy="8897918"/>
+            <a:chOff x="4730115" y="1879078"/>
+            <a:chExt cx="8725065" cy="8103569"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="正方形/長方形 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B945DF4-4807-DD83-FE6D-A22E020EA53E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="正方形/長方形 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAE86F7-ED40-C142-4AD4-A28F50B75186}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2823384"/>
+              <a:ext cx="8508933" cy="1805236"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C7037D3-860C-C58D-AC0F-299DBA81919F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899561" y="4895493"/>
+              <a:ext cx="1027438" cy="372243"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85E61E1C-106C-37E9-C0A1-BBA69266BEAA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="18" idx="1"/>
+              <a:endCxn id="14" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="正方形/長方形 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8AB9CC2-1187-A04F-8E08-52F86CC8C888}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A124CAFD-D2FD-5BB6-3A36-0F7C7E54BC8B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10559655" y="2173455"/>
+              <a:ext cx="1127378" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②特技の例</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="正方形/長方形 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABF2B896-DEBA-76BC-4A98-CF9CE3C2DD91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6510950" y="4866098"/>
+              <a:ext cx="1640081" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③特技の数を設定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9531DF12-26A9-4D7C-CE24-20585C2DD1A7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="5944670" y="5070086"/>
+              <a:ext cx="547825" cy="1195"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="44" name="正方形/長方形 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4921E6F5-3086-5ACA-48AE-1EE7A949899F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899562" y="5378633"/>
+              <a:ext cx="8555618" cy="4604014"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="49" name="正方形/長方形 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7CCB65-8130-C53E-9026-73196F617BCD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10525504" y="4704487"/>
+              <a:ext cx="1179995" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④特技の入力</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="43" name="直線矢印コネクタ 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FC586A4-3CD7-A80B-E848-D2A716BB9339}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="19" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10308427" y="4421918"/>
+            <a:ext cx="488" cy="227653"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="46" name="直線矢印コネクタ 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F48CF319-1286-8005-6CDE-1348AEF0F36D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10308916" y="7215265"/>
+            <a:ext cx="0" cy="260415"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -3487,7 +8420,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72C7325-9D07-4D8F-A95A-46D662A124E8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCF3DBF-5E6A-4390-BF66-A67313761BD1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E0A793-1E11-49B4-8A41-71E6489D3C17}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/スクリーンショット_使い方_エネミー.xlsx
+++ b/スクリーンショット_使い方_エネミー.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K.Housako\dev\lhtrpg_webapp_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442DD976-99CE-4446-9D4D-077C0138EABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6675" yWindow="3945" windowWidth="21585" windowHeight="11295" activeTab="2" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7238,22 +7240,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>71747</xdr:rowOff>
+      <xdr:colOff>395968</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>24121</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>52517</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>89065</xdr:rowOff>
+      <xdr:colOff>271592</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="48" name="グループ化 47">
+        <xdr:cNvPr id="91" name="グループ化 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DF095A9-DF45-22C9-52E4-5DBA06E8D74A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D34AD894-73F6-D0BE-9775-55BC5794939C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7261,18 +7263,158 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="176893" y="2031176"/>
-          <a:ext cx="11441695" cy="10794175"/>
-          <a:chOff x="2628901" y="2760518"/>
-          <a:chExt cx="11534223" cy="10075718"/>
+          <a:off x="395968" y="2595871"/>
+          <a:ext cx="11210374" cy="15739754"/>
+          <a:chOff x="395968" y="2167246"/>
+          <a:chExt cx="11615187" cy="13120379"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="23" name="正方形/長方形 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82EFC521-04B3-A544-B2A4-7B412D68067E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395968" y="2167246"/>
+            <a:ext cx="11615187" cy="13120379"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="25" name="グループ化 24">
+          <xdr:cNvPr id="78" name="グループ化 77">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{679A62CA-420C-4938-2B65-6358357E4B59}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6105164-CEE3-8735-000F-E6787D601891}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7280,158 +7422,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="2628901" y="2760518"/>
-            <a:ext cx="11534223" cy="10075718"/>
-            <a:chOff x="2649683" y="2667000"/>
-            <a:chExt cx="11651986" cy="10685318"/>
+            <a:off x="1857374" y="2727379"/>
+            <a:ext cx="8749542" cy="12248694"/>
+            <a:chOff x="2466975" y="9315450"/>
+            <a:chExt cx="10601325" cy="14944725"/>
           </a:xfrm>
         </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="23" name="正方形/長方形 22">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="75" name="図 74">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82EFC521-04B3-A544-B2A4-7B412D68067E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2649683" y="2667000"/>
-              <a:ext cx="11651986" cy="10685318"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="ja-JP"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="2" name="図 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A6098B-0B2A-2166-4B8F-CC8676042F30}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6386A049-800B-303C-8321-70665D467BA7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7440,16 +7442,18 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill rotWithShape="1">
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect l="7536" t="7445" r="9528"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="3250" t="13128" r="4513"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4069772" y="3186545"/>
-              <a:ext cx="8866909" cy="5998667"/>
+              <a:off x="2466975" y="9315450"/>
+              <a:ext cx="10544175" cy="7564017"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7458,10 +7462,10 @@
         </xdr:pic>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="3" name="図 2">
+            <xdr:cNvPr id="76" name="図 75">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADA2147D-611B-5810-BAFD-F784A0D9A096}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B46A3AEA-0088-3F49-C5A2-2D610BACF850}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7470,16 +7474,50 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill rotWithShape="1">
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:srcRect l="10152" t="33089" r="6017" b="8081"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="5255" t="15043" r="6156"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4069773" y="8978313"/>
-              <a:ext cx="8866910" cy="4200823"/>
+              <a:off x="2562225" y="15169515"/>
+              <a:ext cx="10439400" cy="7299923"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="77" name="図 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E415B419-0472-861A-0E05-E2E5FA0C8931}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="6479" t="14685" r="1118" b="4147"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2505075" y="19442907"/>
+              <a:ext cx="10563225" cy="4817268"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7500,10 +7538,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="4109112" y="3636981"/>
-            <a:ext cx="8460424" cy="8897918"/>
+            <a:off x="1886569" y="3080167"/>
+            <a:ext cx="8519812" cy="11694788"/>
             <a:chOff x="4730115" y="1879078"/>
-            <a:chExt cx="8725065" cy="8103569"/>
+            <a:chExt cx="8725065" cy="10223473"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -7569,7 +7607,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4946247" y="2823384"/>
+              <a:off x="4946247" y="2892788"/>
               <a:ext cx="8508933" cy="1805236"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7619,7 +7657,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4899561" y="4895493"/>
+              <a:off x="4899561" y="5004555"/>
               <a:ext cx="1027438" cy="372243"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7768,7 +7806,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10559655" y="2173455"/>
+              <a:off x="10571255" y="2252774"/>
               <a:ext cx="1127378" cy="420485"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7823,7 +7861,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6510950" y="4866098"/>
+              <a:off x="6510950" y="4975161"/>
               <a:ext cx="1640081" cy="400743"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7878,7 +7916,7 @@
           </xdr:nvCxnSpPr>
           <xdr:spPr>
             <a:xfrm flipH="1">
-              <a:off x="5944670" y="5070086"/>
+              <a:off x="5944670" y="5189064"/>
               <a:ext cx="547825" cy="1195"/>
             </a:xfrm>
             <a:prstGeom prst="straightConnector1">
@@ -7919,8 +7957,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4899562" y="5378633"/>
-              <a:ext cx="8555618" cy="4604014"/>
+              <a:off x="4899562" y="5487695"/>
+              <a:ext cx="8555618" cy="6614856"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7969,8 +8007,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10525504" y="4704487"/>
-              <a:ext cx="1179995" cy="420485"/>
+              <a:off x="10554081" y="4924323"/>
+              <a:ext cx="1151417" cy="420485"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8021,14 +8059,12 @@
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="19" idx="2"/>
-          </xdr:cNvCxnSpPr>
+          <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10308427" y="4421918"/>
-            <a:ext cx="488" cy="227653"/>
+            <a:off x="8129400" y="3987401"/>
+            <a:ext cx="491" cy="237122"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8068,8 +8104,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10308916" y="7215265"/>
-            <a:ext cx="0" cy="260415"/>
+            <a:off x="8129893" y="7036436"/>
+            <a:ext cx="0" cy="156961"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8097,6 +8133,2124 @@
         </xdr:style>
       </xdr:cxnSp>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>205469</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>81093</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="92" name="グループ化 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4EE1B9-3854-DD51-0393-694E77A63B53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12206969" y="3191183"/>
+          <a:ext cx="11210374" cy="5419417"/>
+          <a:chOff x="395968" y="2167246"/>
+          <a:chExt cx="11615187" cy="4513795"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="93" name="正方形/長方形 92">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7216B9D4-3E24-7268-4548-2E7644ED9F13}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395968" y="2167246"/>
+            <a:ext cx="11615187" cy="4513795"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="108" name="図 107">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0796624E-0396-91DD-8DCC-FBC51865925D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+            <a:alphaModFix/>
+          </a:blip>
+          <a:srcRect l="3250" t="13128" r="4513" b="35330"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1857374" y="2727380"/>
+            <a:ext cx="8702375" cy="3678184"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="95" name="グループ化 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C955A8F-68EC-E721-0744-77D18AABC8A3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1886569" y="3080167"/>
+            <a:ext cx="8519812" cy="3224636"/>
+            <a:chOff x="4730115" y="1879078"/>
+            <a:chExt cx="8725065" cy="2818946"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="98" name="正方形/長方形 97">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2F12FE-3488-2BE5-CC06-B89ED41D21B7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="99" name="正方形/長方形 98">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5C213C-91C0-39E9-F74F-364FC65A48B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2892788"/>
+              <a:ext cx="8508933" cy="1805236"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="101" name="直線矢印コネクタ 100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE25A101-CBBE-EE4D-80F8-A063221E6EB6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="102" idx="1"/>
+              <a:endCxn id="98" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="102" name="正方形/長方形 101">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89B3398F-C42A-F694-6EC7-222E6CD36046}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="103" name="正方形/長方形 102">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64C7CDE1-AB9A-A06B-14A1-6AF5EF2E2968}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10571255" y="2252774"/>
+              <a:ext cx="1127378" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②特技の例</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="96" name="直線矢印コネクタ 95">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52C07453-4EC6-8EDB-BC70-5078CC8BB3B3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129400" y="3987401"/>
+            <a:ext cx="491" cy="237122"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>289895</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>17320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>165520</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>209983</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="111" name="グループ化 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6256079B-BFDA-B9BA-64FA-E6ECA96E22EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="22959395" y="2303320"/>
+          <a:ext cx="11210375" cy="10765413"/>
+          <a:chOff x="395968" y="6287489"/>
+          <a:chExt cx="11615187" cy="9000136"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="112" name="正方形/長方形 111">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13E52709-B975-5697-9E89-0E9D62C4915B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395968" y="6287489"/>
+            <a:ext cx="11615187" cy="9000136"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="113" name="グループ化 112">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9706C0E-190C-9B6A-42D8-59F6A9045905}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1857374" y="6440573"/>
+            <a:ext cx="8749542" cy="8535499"/>
+            <a:chOff x="2466975" y="13845947"/>
+            <a:chExt cx="10601325" cy="10414228"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="127" name="図 126">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57A933C4-6CB7-750F-04D8-381DE02681F1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="3250" t="65160" r="4513"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2466975" y="13845947"/>
+              <a:ext cx="10544175" cy="3033518"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="128" name="図 127">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F99216-0C34-BD4A-6BBB-DA43FE3F4C0D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="5255" t="15043" r="6156"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2562225" y="15169515"/>
+              <a:ext cx="10439400" cy="7299923"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="129" name="図 128">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6EC3295-2A98-7B61-A43B-3F57C544A77B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="6479" t="14685" r="1118" b="4147"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2505075" y="19442907"/>
+              <a:ext cx="10563225" cy="4817268"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="114" name="グループ化 113">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5D1BFB5-3899-9E92-CDCA-5E1F4A97B046}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2052029" y="6563669"/>
+            <a:ext cx="8354352" cy="8211285"/>
+            <a:chOff x="4899561" y="4924323"/>
+            <a:chExt cx="8555619" cy="7178228"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="119" name="正方形/長方形 118">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCBC1098-1CF8-9F32-A941-1118A33D4E52}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899561" y="5004555"/>
+              <a:ext cx="1027438" cy="372243"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="123" name="正方形/長方形 122">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CA6B549-A6E4-F0A0-1F4C-8BB71E3374BC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6510950" y="4975161"/>
+              <a:ext cx="1640081" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③特技の数を設定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="124" name="直線矢印コネクタ 123">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9A94C-BB11-C359-40A0-BC2B2A04AA85}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="5944670" y="5189064"/>
+              <a:ext cx="547825" cy="1195"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="125" name="正方形/長方形 124">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE15EDFF-8C50-744C-10C7-947F0E5C9D2E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899562" y="5487695"/>
+              <a:ext cx="8555618" cy="6614856"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="126" name="正方形/長方形 125">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5879082-5CE8-1BAB-310E-FB7ECF463E8C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10554081" y="4924323"/>
+              <a:ext cx="1151417" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④特技の入力</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="116" name="直線矢印コネクタ 115">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCFFEBF2-6768-04EA-6DB1-EFF1F72718FF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129893" y="7036436"/>
+            <a:ext cx="0" cy="156961"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>324660</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>64326</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="グループ化 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E80BDC-2922-458B-9A06-F20B021F03AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="14287500" y="1959429"/>
+          <a:ext cx="11210374" cy="15739754"/>
+          <a:chOff x="395968" y="2167246"/>
+          <a:chExt cx="11615187" cy="13120379"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="正方形/長方形 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D41892C-2AA1-162E-6F6A-9DC91958CF17}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395968" y="2167246"/>
+            <a:ext cx="11615187" cy="13120379"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA69B93-DBE8-1FE1-80F6-EBD0188F44AA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1857374" y="2727379"/>
+            <a:ext cx="8749542" cy="12248694"/>
+            <a:chOff x="2466975" y="9315450"/>
+            <a:chExt cx="10601325" cy="14944725"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF2E5ADB-DAAF-C3F8-A277-5FABB50C8C16}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="3250" t="13128" r="4513"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2466975" y="9315450"/>
+              <a:ext cx="10544175" cy="7564017"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="図 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EC2464-64EC-166D-3DFE-FD51B1218A6C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="5255" t="15043" r="6156"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2562225" y="15169515"/>
+              <a:ext cx="10439400" cy="7299923"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="図 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51812AD5-352D-CA48-2294-DF9E40D6502D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="6479" t="14685" r="1118" b="4147"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2505075" y="19442907"/>
+              <a:ext cx="10563225" cy="4817268"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="8" name="グループ化 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FBBB1CB-E7E6-775C-BFDC-41A02B086957}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1886569" y="3080167"/>
+            <a:ext cx="8519812" cy="11694788"/>
+            <a:chOff x="4730115" y="1879078"/>
+            <a:chExt cx="8725065" cy="10223473"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1887DF6C-8C93-E5D0-6D8A-AF565913EA54}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="正方形/長方形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9BD2C0C-865C-F83A-6472-9B14930F6953}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2892788"/>
+              <a:ext cx="8508933" cy="1805236"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="正方形/長方形 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB97F360-8411-1B95-6619-5940E4476616}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899561" y="5004555"/>
+              <a:ext cx="1027438" cy="372243"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B557CB-2E92-915A-3EB5-CF263DFF03B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="15" idx="1"/>
+              <a:endCxn id="11" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="正方形/長方形 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD6845D6-B76A-D03D-B4AB-E5155FC16344}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04ECFED5-F881-3911-6ADC-8CC1D2D80087}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10571255" y="2252774"/>
+              <a:ext cx="1127378" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②特技の例</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="正方形/長方形 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA60C4F8-C768-0CE8-4F5F-408860A69C8B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6510950" y="4975161"/>
+              <a:ext cx="1640081" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③特技の数を設定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F685B51-CD6E-2BFB-D036-5B8AB5FF597E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="5944670" y="5189064"/>
+              <a:ext cx="547825" cy="1195"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622030DA-63F9-701F-9111-A15B71DA45BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899562" y="5487695"/>
+              <a:ext cx="8555618" cy="6614856"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="正方形/長方形 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F0FC29-C8B1-BE84-A2E7-091D64479FF1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10554081" y="4924323"/>
+              <a:ext cx="1151417" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④特技の入力</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A01B7911-503C-CD0B-80AD-2B4E47637E60}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129400" y="3987401"/>
+            <a:ext cx="491" cy="237122"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82725529-CD90-64B3-4113-46FD09A952BD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129893" y="7036436"/>
+            <a:ext cx="0" cy="156961"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>30388</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>11872</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>137025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C326EA64-3A13-2414-910A-696E327BC751}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect l="4529" t="9225" r="3557"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391102" y="991586"/>
+          <a:ext cx="10301969" cy="7962868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>154214</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>91000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="図 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F542B94-45EB-51AC-0F05-42649FF80ED0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect l="2925" t="34380" r="4032"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1378857" y="8276318"/>
+          <a:ext cx="10341428" cy="5775611"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -8448,4 +10602,25 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F689760-5969-4AFE-B97F-3F688BB232BD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC5A843-566C-4999-B9AB-70A9FADAF3B5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/スクリーンショット_使い方_エネミー.xlsx
+++ b/スクリーンショット_使い方_エネミー.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K.Housako\dev\lhtrpg_webapp_challenge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1807dd80cee582b/ドキュメント/TRPG/01_ログ・ホライズン/ccfolia_駒作成/web_App/lhtrpg_webapp_challenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/スクリーンショット_使い方_エネミー.xlsx
+++ b/スクリーンショット_使い方_エネミー.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1807dd80cee582b/ドキュメント/TRPG/01_ログ・ホライズン/ccfolia_駒作成/web_App/lhtrpg_webapp_challenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A112D909-15C5-4352-A889-E7718AB2D1A7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="4" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -58,12 +58,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -80,8 +86,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -129,8 +138,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1333500" y="1065068"/>
-          <a:ext cx="10806545" cy="22435704"/>
+          <a:off x="1385455" y="935182"/>
+          <a:ext cx="11222181" cy="19015363"/>
           <a:chOff x="3397701" y="1040241"/>
           <a:chExt cx="11335848" cy="19124022"/>
         </a:xfrm>
@@ -1354,8 +1363,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1" y="41771108"/>
-          <a:ext cx="12937286" cy="5890261"/>
+          <a:off x="1" y="35449972"/>
+          <a:ext cx="13430854" cy="5024352"/>
           <a:chOff x="2260630" y="491603"/>
           <a:chExt cx="13585449" cy="5061742"/>
         </a:xfrm>
@@ -2026,8 +2035,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13939492" y="35202669"/>
-          <a:ext cx="12948022" cy="8976360"/>
+          <a:off x="14459037" y="29877328"/>
+          <a:ext cx="13467568" cy="7634201"/>
           <a:chOff x="2258546" y="491603"/>
           <a:chExt cx="13586891" cy="7664485"/>
         </a:xfrm>
@@ -2416,8 +2425,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="48175726"/>
-          <a:ext cx="12939191" cy="8928724"/>
+          <a:off x="0" y="40902090"/>
+          <a:ext cx="13432759" cy="7586565"/>
           <a:chOff x="2258546" y="6676941"/>
           <a:chExt cx="13586891" cy="7615458"/>
         </a:xfrm>
@@ -2806,8 +2815,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14005560" y="47861392"/>
-          <a:ext cx="12916331" cy="8187690"/>
+          <a:off x="14525105" y="40631051"/>
+          <a:ext cx="13435877" cy="6932122"/>
           <a:chOff x="2258546" y="13132769"/>
           <a:chExt cx="13586891" cy="6977784"/>
         </a:xfrm>
@@ -3196,8 +3205,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14434703" y="995795"/>
-          <a:ext cx="10919118" cy="22435704"/>
+          <a:off x="14980226" y="865909"/>
+          <a:ext cx="11360731" cy="19015363"/>
           <a:chOff x="3327725" y="1040241"/>
           <a:chExt cx="11475801" cy="19124022"/>
         </a:xfrm>
@@ -4129,8 +4138,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12620625" y="19339152"/>
-          <a:ext cx="11436931" cy="4626427"/>
+          <a:off x="12494559" y="19112233"/>
+          <a:ext cx="11324872" cy="4573199"/>
           <a:chOff x="3327725" y="3056932"/>
           <a:chExt cx="11475801" cy="4655945"/>
         </a:xfrm>
@@ -4519,8 +4528,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="766763" y="24226919"/>
-          <a:ext cx="11436931" cy="6640884"/>
+          <a:off x="759759" y="23943970"/>
+          <a:ext cx="11324872" cy="6562443"/>
           <a:chOff x="3327725" y="7144405"/>
           <a:chExt cx="11475801" cy="6683747"/>
         </a:xfrm>
@@ -4909,8 +4918,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12734925" y="24422100"/>
-          <a:ext cx="11441694" cy="6918613"/>
+          <a:off x="12608859" y="24136350"/>
+          <a:ext cx="11322631" cy="6837370"/>
           <a:chOff x="3327725" y="13208673"/>
           <a:chExt cx="11475801" cy="6955591"/>
         </a:xfrm>
@@ -5299,8 +5308,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="433388" y="20000460"/>
-          <a:ext cx="11441695" cy="3502478"/>
+          <a:off x="433388" y="19767938"/>
+          <a:ext cx="11322632" cy="3460456"/>
           <a:chOff x="552450" y="20730244"/>
           <a:chExt cx="11322632" cy="3463257"/>
         </a:xfrm>
@@ -5968,15 +5977,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>168088</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>583194</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>213013</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>45311</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>145778</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5991,8 +6000,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190500" y="0"/>
-          <a:ext cx="11441694" cy="19024888"/>
+          <a:off x="336176" y="403412"/>
+          <a:ext cx="11329635" cy="18803572"/>
           <a:chOff x="495300" y="314325"/>
           <a:chExt cx="11441694" cy="19024888"/>
         </a:xfrm>
@@ -7239,6 +7248,999 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>11205</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>335865</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>8297</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="グループ化 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E80BDC-2922-458B-9A06-F20B021F03AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12480296" y="906658"/>
+          <a:ext cx="11408296" cy="15588548"/>
+          <a:chOff x="395968" y="2167246"/>
+          <a:chExt cx="11615187" cy="13120379"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="正方形/長方形 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D41892C-2AA1-162E-6F6A-9DC91958CF17}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="395968" y="2167246"/>
+            <a:ext cx="11615187" cy="13120379"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="lt1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle>
+            <a:defPPr>
+              <a:defRPr lang="ja-JP"/>
+            </a:defPPr>
+            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl1pPr>
+            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl2pPr>
+            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl3pPr>
+            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl4pPr>
+            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl5pPr>
+            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl6pPr>
+            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl7pPr>
+            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl8pPr>
+            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+              <a:defRPr kumimoji="1" sz="1800" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:lvl9pPr>
+          </a:lstStyle>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA69B93-DBE8-1FE1-80F6-EBD0188F44AA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1857374" y="2727379"/>
+            <a:ext cx="8749542" cy="12248694"/>
+            <a:chOff x="2466975" y="9315450"/>
+            <a:chExt cx="10601325" cy="14944725"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF2E5ADB-DAAF-C3F8-A277-5FABB50C8C16}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="3250" t="13128" r="4513"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2466975" y="9315450"/>
+              <a:ext cx="10544175" cy="7564017"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="図 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EC2464-64EC-166D-3DFE-FD51B1218A6C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="5255" t="15043" r="6156"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2562225" y="15169515"/>
+              <a:ext cx="10439400" cy="7299923"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="図 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51812AD5-352D-CA48-2294-DF9E40D6502D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill rotWithShape="1">
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+              <a:alphaModFix/>
+            </a:blip>
+            <a:srcRect l="6479" t="14685" r="1118" b="4147"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2505075" y="19442907"/>
+              <a:ext cx="10563225" cy="4817268"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="8" name="グループ化 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FBBB1CB-E7E6-775C-BFDC-41A02B086957}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="1886569" y="3080167"/>
+            <a:ext cx="8519812" cy="11694788"/>
+            <a:chOff x="4730115" y="1879078"/>
+            <a:chExt cx="8725065" cy="10223473"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1887DF6C-8C93-E5D0-6D8A-AF565913EA54}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4730115" y="1916794"/>
+              <a:ext cx="2578686" cy="357256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="正方形/長方形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9BD2C0C-865C-F83A-6472-9B14930F6953}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4946247" y="2892788"/>
+              <a:ext cx="8508933" cy="1805236"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="正方形/長方形 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB97F360-8411-1B95-6619-5940E4476616}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899561" y="5004555"/>
+              <a:ext cx="1027438" cy="372243"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B557CB-2E92-915A-3EB5-CF263DFF03B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="15" idx="1"/>
+              <a:endCxn id="11" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="7308801" y="2093131"/>
+              <a:ext cx="624821" cy="2291"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="正方形/長方形 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD6845D6-B76A-D03D-B4AB-E5155FC16344}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7933622" y="1879078"/>
+              <a:ext cx="1508759" cy="428106"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①タブの切り替え</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04ECFED5-F881-3911-6ADC-8CC1D2D80087}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10571255" y="2252774"/>
+              <a:ext cx="1127378" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②特技の例</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="正方形/長方形 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA60C4F8-C768-0CE8-4F5F-408860A69C8B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6510950" y="4975161"/>
+              <a:ext cx="1640081" cy="400743"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③特技の数を設定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F685B51-CD6E-2BFB-D036-5B8AB5FF597E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="5944670" y="5189064"/>
+              <a:ext cx="547825" cy="1195"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622030DA-63F9-701F-9111-A15B71DA45BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4899562" y="5487695"/>
+              <a:ext cx="8555618" cy="6614856"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="正方形/長方形 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F0FC29-C8B1-BE84-A2E7-091D64479FF1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10554081" y="4924323"/>
+              <a:ext cx="1151417" cy="420485"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent6"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent6"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④特技の入力</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A01B7911-503C-CD0B-80AD-2B4E47637E60}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129400" y="3987401"/>
+            <a:ext cx="491" cy="237122"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82725529-CD90-64B3-4113-46FD09A952BD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8129893" y="7036436"/>
+            <a:ext cx="0" cy="156961"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>30388</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>11872</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>137025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C326EA64-3A13-2414-910A-696E327BC751}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect l="4529" t="9225" r="3557"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391102" y="991586"/>
+          <a:ext cx="10301969" cy="7962868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>154214</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>91000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="図 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F542B94-45EB-51AC-0F05-42649FF80ED0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect l="2925" t="34380" r="4032"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1378857" y="8276318"/>
+          <a:ext cx="10341428" cy="5775611"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>395968</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -7263,8 +8265,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="395968" y="2595871"/>
-          <a:ext cx="11210374" cy="15739754"/>
+          <a:off x="395968" y="2167246"/>
+          <a:ext cx="11615187" cy="13120379"/>
           <a:chOff x="395968" y="2167246"/>
           <a:chExt cx="11615187" cy="13120379"/>
         </a:xfrm>
@@ -8161,8 +9163,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12206969" y="3191183"/>
-          <a:ext cx="11210374" cy="5419417"/>
+          <a:off x="12635594" y="2667308"/>
+          <a:ext cx="11615187" cy="4514542"/>
           <a:chOff x="395968" y="2167246"/>
           <a:chExt cx="11615187" cy="4513795"/>
         </a:xfrm>
@@ -8683,8 +9685,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="22959395" y="2303320"/>
-          <a:ext cx="11210375" cy="10765413"/>
+          <a:off x="23769020" y="1922320"/>
+          <a:ext cx="11615188" cy="9003288"/>
           <a:chOff x="395968" y="6287489"/>
           <a:chExt cx="11615187" cy="9000136"/>
         </a:xfrm>
@@ -9263,27 +10265,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>586874</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>222926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>324660</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>64326</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>279034</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>207065</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="グループ化 4">
+        <xdr:cNvPr id="226" name="グループ化 225">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E80BDC-2922-458B-9A06-F20B021F03AA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD160C9-9824-AD0E-44D5-A3E1CD37F8C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9291,18 +10293,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14287500" y="1959429"/>
-          <a:ext cx="11210374" cy="15739754"/>
-          <a:chOff x="395968" y="2167246"/>
-          <a:chExt cx="11615187" cy="13120379"/>
+          <a:off x="586874" y="1413551"/>
+          <a:ext cx="7235960" cy="15462264"/>
+          <a:chOff x="586874" y="1365926"/>
+          <a:chExt cx="7235960" cy="14843139"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <xdr:cNvPr id="7" name="正方形/長方形 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D41892C-2AA1-162E-6F6A-9DC91958CF17}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BDEB930-E198-11B1-9E26-54DB96182DB9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9310,158 +10312,161 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="395968" y="2167246"/>
-            <a:ext cx="11615187" cy="13120379"/>
+            <a:off x="586874" y="1365926"/>
+            <a:ext cx="7235960" cy="14843139"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="2">
-            <a:schemeClr val="dk1"/>
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
           </a:lnRef>
           <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="accent1"/>
           </a:fillRef>
           <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
+            <a:schemeClr val="accent1"/>
           </a:effectRef>
           <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
+            <a:schemeClr val="lt1"/>
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="ja-JP"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr kumimoji="1" sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="dk1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US"/>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="7" name="グループ化 6">
+          <xdr:cNvPr id="2" name="グループ化 1">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFA69B93-DBE8-1FE1-80F6-EBD0188F44AA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9BD2DDE-D380-086C-06B9-971205894338}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks noChangeAspect="1"/>
+          </xdr:cNvGrpSpPr>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1857374" y="2727379"/>
-            <a:ext cx="8749542" cy="12248694"/>
-            <a:chOff x="2466975" y="9315450"/>
-            <a:chExt cx="10601325" cy="14944725"/>
+            <a:off x="642954" y="1412309"/>
+            <a:ext cx="7123800" cy="14738485"/>
+            <a:chOff x="2545557" y="-2378679"/>
+            <a:chExt cx="7013517" cy="15555882"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="21" name="図 20">
+            <xdr:cNvPr id="3" name="図 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF2E5ADB-DAAF-C3F8-A277-5FABB50C8C16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3C3AB3-454B-934F-A125-56AD37D3BA84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect l="20878" t="12904" r="21613"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2545557" y="-2378679"/>
+              <a:ext cx="7011386" cy="5707604"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="図 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCD2B91D-A529-2F05-8253-C6505020D97F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:srcRect l="20878" t="18033" r="21613"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2547124" y="2400301"/>
+              <a:ext cx="7011407" cy="5371613"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="図 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D0EB867-6FF5-8789-5823-B03AD1D7D28C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:srcRect l="20878" t="11685" r="21613" b="1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2547134" y="5797550"/>
+              <a:ext cx="7011402" cy="5787479"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="図 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E27F2A-3857-262B-1963-0E0E3AF0FFD2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9470,82 +10475,16 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill rotWithShape="1">
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-              <a:alphaModFix/>
-            </a:blip>
-            <a:srcRect l="3250" t="13128" r="4513"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:srcRect l="20880" t="18532" r="21612" b="4803"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2466975" y="9315450"/>
-              <a:ext cx="10544175" cy="7564017"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="22" name="図 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EC2464-64EC-166D-3DFE-FD51B1218A6C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill rotWithShape="1">
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-              <a:alphaModFix/>
-            </a:blip>
-            <a:srcRect l="5255" t="15043" r="6156"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2562225" y="15169515"/>
-              <a:ext cx="10439400" cy="7299923"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="23" name="図 22">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51812AD5-352D-CA48-2294-DF9E40D6502D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill rotWithShape="1">
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-              <a:alphaModFix/>
-            </a:blip>
-            <a:srcRect l="6479" t="14685" r="1118" b="4147"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2505075" y="19442907"/>
-              <a:ext cx="10563225" cy="4817268"/>
+              <a:off x="2545558" y="8151789"/>
+              <a:ext cx="7013516" cy="5025414"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9553,551 +10492,77 @@
           </xdr:spPr>
         </xdr:pic>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="8" name="グループ化 7">
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="141" name="正方形/長方形 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FBBB1CB-E7E6-775C-BFDC-41A02B086957}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59E3523C-C975-3D3E-85D9-B25DFF572188}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="1886569" y="3080167"/>
-            <a:ext cx="8519812" cy="11694788"/>
-            <a:chOff x="4730115" y="1879078"/>
-            <a:chExt cx="8725065" cy="10223473"/>
+            <a:off x="676161" y="1716087"/>
+            <a:ext cx="1922619" cy="303281"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="正方形/長方形 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1887DF6C-8C93-E5D0-6D8A-AF565913EA54}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4730115" y="1916794"/>
-              <a:ext cx="2578686" cy="357256"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="正方形/長方形 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9BD2C0C-865C-F83A-6472-9B14930F6953}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4946247" y="2892788"/>
-              <a:ext cx="8508933" cy="1805236"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="13" name="正方形/長方形 12">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB97F360-8411-1B95-6619-5940E4476616}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4899561" y="5004555"/>
-              <a:ext cx="1027438" cy="372243"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B557CB-2E92-915A-3EB5-CF263DFF03B0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr>
-              <a:stCxn id="15" idx="1"/>
-              <a:endCxn id="11" idx="3"/>
-            </xdr:cNvCxnSpPr>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm flipH="1">
-              <a:off x="7308801" y="2093131"/>
-              <a:ext cx="624821" cy="2291"/>
-            </a:xfrm>
-            <a:prstGeom prst="straightConnector1">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:tailEnd type="triangle"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="正方形/長方形 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD6845D6-B76A-D03D-B4AB-E5155FC16344}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7933622" y="1879078"/>
-              <a:ext cx="1508759" cy="428106"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="FF0000"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>①タブの切り替え</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="正方形/長方形 15">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04ECFED5-F881-3911-6ADC-8CC1D2D80087}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10571255" y="2252774"/>
-              <a:ext cx="1127378" cy="420485"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="FF0000"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>②特技の例</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="正方形/長方形 16">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA60C4F8-C768-0CE8-4F5F-408860A69C8B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6510950" y="4975161"/>
-              <a:ext cx="1640081" cy="400743"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="FF0000"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>③特技の数を設定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F685B51-CD6E-2BFB-D036-5B8AB5FF597E}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr/>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm flipH="1">
-              <a:off x="5944670" y="5189064"/>
-              <a:ext cx="547825" cy="1195"/>
-            </a:xfrm>
-            <a:prstGeom prst="straightConnector1">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:tailEnd type="triangle"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="19" name="正方形/長方形 18">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622030DA-63F9-701F-9111-A15B71DA45BE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4899562" y="5487695"/>
-              <a:ext cx="8555618" cy="6614856"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="正方形/長方形 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F0FC29-C8B1-BE84-A2E7-091D64479FF1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10554081" y="4924323"/>
-              <a:ext cx="1151417" cy="420485"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent6"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent6"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="FF0000"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>④特技の入力</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <xdr:cNvPr id="144" name="直線矢印コネクタ 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A01B7911-503C-CD0B-80AD-2B4E47637E60}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F356751-6A2A-0088-865A-4C0B2770F0FE}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
           <xdr:cNvCxnSpPr/>
         </xdr:nvCxnSpPr>
         <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8129400" y="3987401"/>
-            <a:ext cx="491" cy="237122"/>
+          <a:xfrm flipH="1">
+            <a:off x="2612334" y="1870214"/>
+            <a:ext cx="296518" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
           </a:prstGeom>
-          <a:ln w="28575">
+          <a:ln w="38100">
             <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
@@ -10119,12 +10584,132 @@
           </a:fontRef>
         </xdr:style>
       </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="146" name="正方形/長方形 145">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD6A8DA8-5538-0254-B624-82C975705896}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2914123" y="1716087"/>
+            <a:ext cx="1185769" cy="303281"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>タブの切り替え</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="147" name="正方形/長方形 146">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9D24FA2-623B-AF72-AA80-D5E185CF79CA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6735417" y="1682957"/>
+            <a:ext cx="1010176" cy="303281"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <xdr:cNvPr id="148" name="直線矢印コネクタ 147">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82725529-CD90-64B3-4113-46FD09A952BD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{423788DB-EAD7-2967-1936-5CBA49202BC5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10132,13 +10717,644 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8129893" y="7036436"/>
-            <a:ext cx="0" cy="156961"/>
+            <a:off x="6124161" y="1837084"/>
+            <a:ext cx="611255" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
           </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="149" name="正方形/長方形 148">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{101B2967-7B3A-8BBF-09CF-4B7D17E5B60C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5148469" y="1682957"/>
+            <a:ext cx="1305341" cy="303281"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
           <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>入力内容をクリア</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="151" name="正方形/長方形 150">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5CFD43-9A65-4631-A723-1573A87B92EB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="826603" y="2528652"/>
+            <a:ext cx="992258" cy="331387"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="152" name="直線矢印コネクタ 151">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518CDA05-E80C-FED7-2280-453228BFE525}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1846722" y="2700143"/>
+            <a:ext cx="296517" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="153" name="正方形/長方形 152">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D48CB0A-9B1C-497A-BA1D-25F933A7C3FF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2148509" y="2542705"/>
+            <a:ext cx="1446142" cy="303280"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>入力内容の読み込み</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="154" name="正方形/長方形 153">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F227F5C-615C-E984-CAEF-3631D912A0F4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="760342" y="2980881"/>
+            <a:ext cx="6859658" cy="2924618"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="162" name="正方形/長方形 161">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61AD6498-2A57-1D00-550B-10A294E0EC51}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="760342" y="6200331"/>
+            <a:ext cx="6859658" cy="4867719"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="163" name="正方形/長方形 162">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90B131B5-F8F2-1424-7CA4-9A62F441314D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="760342" y="11334749"/>
+            <a:ext cx="6859658" cy="4676775"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="164" name="正方形/長方形 163">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD2B3D0-6E0B-3538-B431-2837A44D5583}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1662826" y="10606957"/>
+            <a:ext cx="1021363" cy="541256"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>エネミー</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>能力値欄</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="165" name="直線矢印コネクタ 164">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5554E339-3A32-CAA2-7A3C-2F11CB5A64C2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="164" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2173508" y="11148213"/>
+            <a:ext cx="0" cy="196062"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="166" name="正方形/長方形 165">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F554B5-3694-DF5C-8868-459D843B5AF9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1057275" y="5676900"/>
+            <a:ext cx="1108516" cy="342970"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>ドロップ品欄</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="167" name="直線矢印コネクタ 166">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BE7C69D-E55C-6AD4-8145-997811C56634}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="166" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1611533" y="6019870"/>
+            <a:ext cx="0" cy="180905"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
             <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
@@ -10163,94 +11379,1639 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>30388</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>11872</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>627715</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>222926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>137025</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>317931</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>74544</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="225" name="グループ化 224">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C326EA64-3A13-2414-910A-696E327BC751}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CE7129E-C485-D751-1EAD-82D981FE1427}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:srcRect l="4529" t="9225" r="3557"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1391102" y="991586"/>
-          <a:ext cx="10301969" cy="7962868"/>
+          <a:off x="8171515" y="1413551"/>
+          <a:ext cx="7234016" cy="10090993"/>
+          <a:chOff x="8247715" y="1435199"/>
+          <a:chExt cx="7310216" cy="10277163"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="正方形/長方形 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9394109F-090A-0FAF-2A40-751017499C7A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8247715" y="1435199"/>
+            <a:ext cx="7310216" cy="10277163"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="8" name="グループ化 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0D2CCB0-3BD7-2E0E-B604-B771EEFDD85A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks noChangeAspect="1"/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="8302823" y="1495436"/>
+            <a:ext cx="7200000" cy="10159309"/>
+            <a:chOff x="2545555" y="75127"/>
+            <a:chExt cx="7011395" cy="10194941"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="図 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFAC8EC-3B4C-52C4-651D-8C9963CF71E6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:srcRect l="20879" t="12904" r="21614"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2545556" y="75127"/>
+              <a:ext cx="7011393" cy="5707605"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="10" name="図 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9413DCEF-89E2-15D2-58A1-E670BAA0685C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:srcRect l="20878" t="20627" r="21613" b="4695"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2545555" y="5376334"/>
+              <a:ext cx="7011395" cy="4893734"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="177" name="正方形/長方形 176">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7446EAB-0C55-65FA-E2C2-654F96B28AD7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8390173" y="1813069"/>
+            <a:ext cx="1931031" cy="317135"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="178" name="直線矢印コネクタ 177">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{419DF90B-F6E6-EABD-B090-65A28B50B8A5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="10334758" y="1981050"/>
+            <a:ext cx="303446" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="179" name="正方形/長方形 178">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{863A34FC-4261-2CE4-FFFB-3E886E385DF5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10643475" y="1813069"/>
+            <a:ext cx="1205067" cy="317135"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>タブの切り替え</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="183" name="正方形/長方形 182">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F45778-3DF1-93A4-85AD-4F87E4252576}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8414483" y="2607799"/>
+            <a:ext cx="6928932" cy="1718036"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="184" name="正方形/長方形 183">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F558ABA6-7736-7C3D-3CB5-90F11BE4EE90}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8414483" y="5012377"/>
+            <a:ext cx="6928932" cy="6504214"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="190" name="正方形/長方形 189">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFFC7060-BAC8-07C9-630A-34EFFB2A794D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12777506" y="1893547"/>
+            <a:ext cx="784363" cy="435149"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>特技の例</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="191" name="直線矢印コネクタ 190">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA44D587-66B7-A012-6428-94F0254975DE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="190" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13173151" y="2328696"/>
+            <a:ext cx="0" cy="248249"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="198" name="直線矢印コネクタ 197">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95688B4B-5C66-1798-1E82-A5512AF2A220}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="9318651" y="4665632"/>
+            <a:ext cx="291074" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="199" name="正方形/長方形 198">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CD89030-D0E3-AEFB-D266-4C0BEFEDB52B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9614995" y="4510669"/>
+            <a:ext cx="1472367" cy="310331"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>入力内容の読み込み</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="200" name="正方形/長方形 199">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCA331D0-F978-3E80-706B-C1B4FB105940}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8481257" y="4382047"/>
+            <a:ext cx="796538" cy="541709"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="205" name="正方形/長方形 204">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1350FB61-77C8-CA81-5781-4EB8307B6A13}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12863232" y="4278872"/>
+            <a:ext cx="612911" cy="435149"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>特技</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="206" name="直線矢印コネクタ 205">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{442D09D2-6DCC-E65F-096F-9D119FFB72CC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="205" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="13173151" y="4714021"/>
+            <a:ext cx="1121" cy="235923"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>18143</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>193675</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>675569</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>222925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>154214</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>91000</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>355110</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="224" name="グループ化 223">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F542B94-45EB-51AC-0F05-42649FF80ED0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A29409CD-B1B8-166D-0E3B-188458628CAF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:srcRect l="2925" t="34380" r="4032"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1378857" y="8276318"/>
-          <a:ext cx="10341428" cy="5775611"/>
+          <a:off x="15763169" y="1413550"/>
+          <a:ext cx="7223341" cy="8063824"/>
+          <a:chOff x="15915569" y="1435198"/>
+          <a:chExt cx="7299541" cy="8211028"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="正方形/長方形 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F21B30-B243-35B7-58F9-67CF01A38F97}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="15915569" y="1435198"/>
+            <a:ext cx="7299541" cy="8211028"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="11" name="グループ化 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24AC3170-354E-77EE-7F36-3479C3AB7E58}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks noChangeAspect="1"/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="15965339" y="1495436"/>
+            <a:ext cx="7200000" cy="8081443"/>
+            <a:chOff x="2545554" y="-720737"/>
+            <a:chExt cx="7011398" cy="8095203"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="図 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEBCC856-D25B-CD91-FD2D-168CDEF4A727}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+            <a:srcRect l="20879" t="13670" r="21614"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2545556" y="-720737"/>
+              <a:ext cx="7011396" cy="5657413"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="13" name="図 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64CCC063-5CA4-FEF7-E700-68CB6864080A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:srcRect l="20881" t="53004" r="21613" b="4876"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2545554" y="4614333"/>
+              <a:ext cx="7011398" cy="2760133"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="180" name="正方形/長方形 179">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08051045-FF9D-DC06-4BD4-995B3A5B83F7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16010173" y="1813069"/>
+            <a:ext cx="1931030" cy="317135"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="181" name="直線矢印コネクタ 180">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA70F167-0EFB-B939-A0F2-1058A1CEEA93}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="17954757" y="1981050"/>
+            <a:ext cx="303446" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="182" name="正方形/長方形 181">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44905957-D746-D1FA-BB6A-70F1173D6FCA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18263474" y="1813069"/>
+            <a:ext cx="1205067" cy="317135"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>タブの切り替え</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="185" name="正方形/長方形 184">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8F14A19-DE32-7587-EC57-B5BCA3FB4FD2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16088911" y="2607799"/>
+            <a:ext cx="6928931" cy="4117768"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="210" name="正方形/長方形 209">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1A4BDE6-3A83-4455-C0AD-C7CF2B8CFECF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16088911" y="7101939"/>
+            <a:ext cx="6928931" cy="1738002"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="215" name="正方形/長方形 214">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{367CF89E-CC0D-6640-53D5-79074794387A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20934218" y="8956963"/>
+            <a:ext cx="2049607" cy="380134"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="216" name="直線矢印コネクタ 215">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{450397AD-9057-C8F0-8DDC-449A80C67B7A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20289823" y="9158395"/>
+            <a:ext cx="618181" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="217" name="正方形/長方形 216">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0093B87E-1202-A2D1-7A65-E808A72E1730}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="19051019" y="8997545"/>
+            <a:ext cx="1566210" cy="317136"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>データファイル出力</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="218" name="正方形/長方形 217">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C5A71AF-8548-A358-3E6E-E9318F33689C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="20257180" y="1899150"/>
+            <a:ext cx="1567244" cy="435149"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>エネミーデータ確認</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="219" name="直線矢印コネクタ 218">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A9A2A35-EEC5-020D-A30F-176424242385}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="218" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="21039681" y="2334299"/>
+            <a:ext cx="1121" cy="235923"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="220" name="正方形/長方形 219">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B20B009A-6520-87A1-5B56-FC4465E0E823}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16506725" y="6427345"/>
+            <a:ext cx="1203663" cy="435149"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>CCFOLIA</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>用出力</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="221" name="直線矢印コネクタ 220">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E30A464E-02DC-FDAF-AC4E-5728C55FFA5C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="220" idx="2"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="17107436" y="6862494"/>
+            <a:ext cx="1121" cy="235924"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10594,7 +13355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E0A793-1E11-49B4-8A41-71E6489D3C17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F689760-5969-4AFE-B97F-3F688BB232BD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
@@ -10605,7 +13366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F689760-5969-4AFE-B97F-3F688BB232BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E0A793-1E11-49B4-8A41-71E6489D3C17}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
@@ -10619,8 +13380,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC5A843-566C-4999-B9AB-70A9FADAF3B5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/スクリーンショット_使い方_エネミー.xlsx
+++ b/スクリーンショット_使い方_エネミー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1807dd80cee582b/ドキュメント/TRPG/01_ログ・ホライズン/ccfolia_駒作成/web_App/lhtrpg_webapp_challenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A112D909-15C5-4352-A889-E7718AB2D1A7}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{6B15DEAE-8708-4288-ABA9-FAE3B4419C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB4F72B-6CF7-4FDE-AB32-413CD3C8D284}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="4" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{6B444F69-8995-4414-BA93-D2B24FFF7C87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,8 +138,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1385455" y="935182"/>
-          <a:ext cx="11222181" cy="19015363"/>
+          <a:off x="1330036" y="914400"/>
+          <a:ext cx="10778836" cy="18468108"/>
           <a:chOff x="3397701" y="1040241"/>
           <a:chExt cx="11335848" cy="19124022"/>
         </a:xfrm>
@@ -1363,8 +1363,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1" y="35449972"/>
-          <a:ext cx="13430854" cy="5024352"/>
+          <a:off x="1" y="34438590"/>
+          <a:ext cx="12904381" cy="4885806"/>
           <a:chOff x="2260630" y="491603"/>
           <a:chExt cx="13585449" cy="5061742"/>
         </a:xfrm>
@@ -2035,8 +2035,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14459037" y="29877328"/>
-          <a:ext cx="13467568" cy="7634201"/>
+          <a:off x="13904856" y="29025274"/>
+          <a:ext cx="12913385" cy="7419455"/>
           <a:chOff x="2258546" y="491603"/>
           <a:chExt cx="13586891" cy="7664485"/>
         </a:xfrm>
@@ -2425,8 +2425,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="40902090"/>
-          <a:ext cx="13432759" cy="7586565"/>
+          <a:off x="0" y="39738308"/>
+          <a:ext cx="12906286" cy="7356579"/>
           <a:chOff x="2258546" y="6676941"/>
           <a:chExt cx="13586891" cy="7615458"/>
         </a:xfrm>
@@ -2815,8 +2815,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14525105" y="40631051"/>
-          <a:ext cx="13435877" cy="6932122"/>
+          <a:off x="13970924" y="39474197"/>
+          <a:ext cx="12881694" cy="6731230"/>
           <a:chOff x="2258546" y="13132769"/>
           <a:chExt cx="13586891" cy="6977784"/>
         </a:xfrm>
@@ -3205,8 +3205,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14980226" y="865909"/>
-          <a:ext cx="11360731" cy="19015363"/>
+          <a:off x="14398335" y="845127"/>
+          <a:ext cx="10889677" cy="18468108"/>
           <a:chOff x="3327725" y="1040241"/>
           <a:chExt cx="11475801" cy="19124022"/>
         </a:xfrm>
@@ -4138,8 +4138,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12494559" y="19112233"/>
-          <a:ext cx="11324872" cy="4573199"/>
+          <a:off x="12292853" y="18930698"/>
+          <a:ext cx="11145578" cy="4530616"/>
           <a:chOff x="3327725" y="3056932"/>
           <a:chExt cx="11475801" cy="4655945"/>
         </a:xfrm>
@@ -4528,8 +4528,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="759759" y="23943970"/>
-          <a:ext cx="11324872" cy="6562443"/>
+          <a:off x="748553" y="23717612"/>
+          <a:ext cx="11145578" cy="6499690"/>
           <a:chOff x="3327725" y="7144405"/>
           <a:chExt cx="11475801" cy="6683747"/>
         </a:xfrm>
@@ -4918,8 +4918,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12608859" y="24136350"/>
-          <a:ext cx="11322631" cy="6837370"/>
+          <a:off x="12407153" y="23907750"/>
+          <a:ext cx="11132131" cy="6772376"/>
           <a:chOff x="3327725" y="13208673"/>
           <a:chExt cx="11475801" cy="6955591"/>
         </a:xfrm>
@@ -5308,8 +5308,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="433388" y="19767938"/>
-          <a:ext cx="11322632" cy="3460456"/>
+          <a:off x="433388" y="19574300"/>
+          <a:ext cx="11132132" cy="3434459"/>
           <a:chOff x="552450" y="20730244"/>
           <a:chExt cx="11322632" cy="3463257"/>
         </a:xfrm>
@@ -6000,8 +6000,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="336176" y="403412"/>
-          <a:ext cx="11329635" cy="18803572"/>
+          <a:off x="336176" y="401170"/>
+          <a:ext cx="11139135" cy="18624279"/>
           <a:chOff x="495300" y="314325"/>
           <a:chExt cx="11441694" cy="19024888"/>
         </a:xfrm>
@@ -7272,8 +7272,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12480296" y="906658"/>
-          <a:ext cx="11408296" cy="15588548"/>
+          <a:off x="11981532" y="885876"/>
+          <a:ext cx="10964951" cy="15138276"/>
           <a:chOff x="395968" y="2167246"/>
           <a:chExt cx="11615187" cy="13120379"/>
         </a:xfrm>
@@ -8265,8 +8265,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="395968" y="2167246"/>
-          <a:ext cx="11615187" cy="13120379"/>
+          <a:off x="395968" y="2081521"/>
+          <a:ext cx="11210374" cy="12596504"/>
           <a:chOff x="395968" y="2167246"/>
           <a:chExt cx="11615187" cy="13120379"/>
         </a:xfrm>
@@ -9163,8 +9163,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12635594" y="2667308"/>
-          <a:ext cx="11615187" cy="4514542"/>
+          <a:off x="12206969" y="2562533"/>
+          <a:ext cx="11210374" cy="4333567"/>
           <a:chOff x="395968" y="2167246"/>
           <a:chExt cx="11615187" cy="4513795"/>
         </a:xfrm>
@@ -9685,8 +9685,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="23769020" y="1922320"/>
-          <a:ext cx="11615188" cy="9003288"/>
+          <a:off x="22959395" y="1846120"/>
+          <a:ext cx="11210375" cy="8650863"/>
           <a:chOff x="395968" y="6287489"/>
           <a:chExt cx="11615187" cy="9000136"/>
         </a:xfrm>
@@ -10271,14 +10271,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>586874</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>222926</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>279034</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>207065</xdr:rowOff>
+      <xdr:rowOff>207064</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -10293,8 +10293,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="586874" y="1413551"/>
-          <a:ext cx="7235960" cy="15462264"/>
+          <a:off x="586874" y="1329054"/>
+          <a:ext cx="7262999" cy="14363816"/>
           <a:chOff x="586874" y="1365926"/>
           <a:chExt cx="7235960" cy="14843139"/>
         </a:xfrm>
@@ -10318,27 +10318,20 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:sysClr val="window" lastClr="FFFFFF"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
+          <a:ln/>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
+            <a:schemeClr val="dk1"/>
           </a:lnRef>
           <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="lt1"/>
           </a:fillRef>
           <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="dk1"/>
           </a:effectRef>
           <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="dk1"/>
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
@@ -11382,15 +11375,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>627715</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>222926</xdr:rowOff>
+      <xdr:colOff>410968</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>317931</xdr:colOff>
+      <xdr:colOff>101184</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>74544</xdr:rowOff>
+      <xdr:rowOff>74543</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -11405,8 +11398,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8171515" y="1413551"/>
-          <a:ext cx="7234016" cy="10090993"/>
+          <a:off x="7981807" y="1329054"/>
+          <a:ext cx="7261054" cy="9364328"/>
           <a:chOff x="8247715" y="1435199"/>
           <a:chExt cx="7310216" cy="10277163"/>
         </a:xfrm>
@@ -11430,27 +11423,20 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:sysClr val="window" lastClr="FFFFFF"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
+          <a:ln/>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
+            <a:schemeClr val="dk1"/>
           </a:lnRef>
           <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="lt1"/>
           </a:fillRef>
           <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="dk1"/>
           </a:effectRef>
           <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="dk1"/>
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
@@ -12198,13 +12184,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>675569</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>222925</xdr:rowOff>
+      <xdr:colOff>233117</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>355110</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>600916</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
@@ -12221,8 +12207,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15763169" y="1413550"/>
-          <a:ext cx="7223341" cy="8063824"/>
+          <a:off x="15374794" y="1329054"/>
+          <a:ext cx="7250380" cy="7489251"/>
           <a:chOff x="15915569" y="1435198"/>
           <a:chExt cx="7299541" cy="8211028"/>
         </a:xfrm>
@@ -12246,27 +12232,20 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:sysClr val="window" lastClr="FFFFFF"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
+          <a:ln/>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
+            <a:schemeClr val="dk1"/>
           </a:lnRef>
           <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="lt1"/>
           </a:fillRef>
           <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="dk1"/>
           </a:effectRef>
           <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="dk1"/>
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
@@ -13014,7 +12993,2727 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>122904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>14042</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>107042</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="137" name="グループ化 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D1EF9C4-CF2A-15F9-0E81-84DE2C6E8F97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="27530323" y="1007807"/>
+          <a:ext cx="22038300" cy="14363816"/>
+          <a:chOff x="27530323" y="1007807"/>
+          <a:chExt cx="22038300" cy="14363816"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="16" name="グループ化 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{085104A9-5D58-4BC8-B5AA-CB6357074F43}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="27530323" y="1007807"/>
+            <a:ext cx="7262999" cy="14363816"/>
+            <a:chOff x="586874" y="1365926"/>
+            <a:chExt cx="7235960" cy="14843139"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="正方形/長方形 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B31F37-58FD-2094-6159-1C5ADEB2E28E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="586874" y="1365926"/>
+              <a:ext cx="7235960" cy="14843139"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="18" name="グループ化 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97B6B564-0715-BD98-B78A-6C1A4C3707A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr>
+              <a:grpSpLocks noChangeAspect="1"/>
+            </xdr:cNvGrpSpPr>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="642954" y="1412309"/>
+              <a:ext cx="7123800" cy="14738485"/>
+              <a:chOff x="2545557" y="-2378679"/>
+              <a:chExt cx="7013517" cy="15555882"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="35" name="図 34">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD06D2AA-81A0-1EFF-CAC2-7B0254324B46}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+              <a:srcRect l="20878" t="12904" r="21613"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545557" y="-2378679"/>
+                <a:ext cx="7011386" cy="5707604"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="36" name="図 35">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC657DF-41C5-AA8A-9E65-E5F5C5C5FCA0}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+              <a:srcRect l="20878" t="18033" r="21613"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2547124" y="2400301"/>
+                <a:ext cx="7011407" cy="5371613"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="37" name="図 36">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FE5E92C-D7E5-2FCD-7129-330E9E1BD31E}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+              <a:srcRect l="20878" t="11685" r="21613" b="1"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2547134" y="5797550"/>
+                <a:ext cx="7011402" cy="5787479"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="38" name="図 37">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E3CF41B-855B-1962-06B4-E5CEC7D8B495}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill rotWithShape="1">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+              <a:srcRect l="20880" t="18532" r="21612" b="4803"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545558" y="8151789"/>
+                <a:ext cx="7013516" cy="5025414"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC9D7AA-9FB6-94D0-731C-BA1032EAAE8F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="676161" y="1716087"/>
+              <a:ext cx="1922619" cy="303281"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="20" name="直線矢印コネクタ 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCC3CCF5-3D92-1E4F-F4A0-A86CA74A9656}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="2612334" y="1870214"/>
+              <a:ext cx="296518" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="正方形/長方形 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C226F6-CF86-87B9-6576-C45CFCA6227E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2914123" y="1716087"/>
+              <a:ext cx="1185769" cy="303281"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>タブの切り替え</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="正方形/長方形 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA5C9E43-0A87-4E6F-B967-F20485402328}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6735417" y="1682957"/>
+              <a:ext cx="1010176" cy="303281"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BF4C6B1-9A02-287D-549F-7A6F681899F1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6124161" y="1837084"/>
+              <a:ext cx="611255" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="正方形/長方形 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CF3CCB2-37EC-4B80-7D7C-B962D68838FB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5148469" y="1682957"/>
+              <a:ext cx="1305341" cy="303281"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>入力内容をクリア</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="正方形/長方形 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A4162A5-B2A1-7E95-E932-B060E40691C9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="826603" y="2528652"/>
+              <a:ext cx="992258" cy="331387"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="26" name="直線矢印コネクタ 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06DDBA91-AC92-6F7D-E13C-063C0EC9EFCC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="1846722" y="2700143"/>
+              <a:ext cx="296517" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="正方形/長方形 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{862A54C5-B4EA-5707-7BD8-CC7A4D1B10A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2148509" y="2542705"/>
+              <a:ext cx="1446142" cy="303280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>入力内容の読み込み</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="正方形/長方形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E1C8ED4-64E8-195D-FF7B-06819EB17086}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="760342" y="2980881"/>
+              <a:ext cx="6859658" cy="2924618"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="正方形/長方形 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{946284A8-B85D-B118-1377-46C65EC4D751}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="760342" y="6200331"/>
+              <a:ext cx="6859658" cy="4867719"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="30" name="正方形/長方形 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDBBFB33-1377-75DB-134B-3CB93A1DC1B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="760342" y="11334749"/>
+              <a:ext cx="6859658" cy="4676775"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="正方形/長方形 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE10CE6-E1AB-50D8-FCAA-F9DBDB7F021E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1662826" y="10606957"/>
+              <a:ext cx="1021363" cy="541256"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>エネミー</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>能力値欄</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="32" name="直線矢印コネクタ 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7571357A-D66D-E378-A150-351B1A2DCFC1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="31" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2173508" y="11148213"/>
+              <a:ext cx="0" cy="196062"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="33" name="正方形/長方形 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCEBBDA7-223C-B9E4-BE86-D03E96C12D68}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1057275" y="5676900"/>
+              <a:ext cx="1108516" cy="342970"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>ドロップ品欄</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="34" name="直線矢印コネクタ 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CCD5DFE-55C2-D79F-E8BE-91EE951C7DD4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="33" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1611533" y="6019870"/>
+              <a:ext cx="0" cy="180905"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="39" name="グループ化 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD5FA359-5D2A-4480-BD37-721F357A40E6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="34925256" y="1007807"/>
+            <a:ext cx="7261054" cy="9364328"/>
+            <a:chOff x="8247715" y="1435199"/>
+            <a:chExt cx="7310216" cy="10277163"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="40" name="正方形/長方形 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4E43C84-F4AA-9DCE-53EF-94C34676925E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8247715" y="1435199"/>
+              <a:ext cx="7310216" cy="10277163"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="41" name="グループ化 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54CBEF38-B9D3-1A02-F029-78B345A7AFF6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr>
+              <a:grpSpLocks noChangeAspect="1"/>
+            </xdr:cNvGrpSpPr>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8302823" y="1495436"/>
+              <a:ext cx="7200000" cy="10159309"/>
+              <a:chOff x="2545555" y="75127"/>
+              <a:chExt cx="7011395" cy="10194941"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="54" name="図 53">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5C35AD-3931-2E84-F95D-D6D56040D890}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+              <a:srcRect l="20879" t="12904" r="21614"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545556" y="75127"/>
+                <a:ext cx="7011393" cy="5707605"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="55" name="図 54">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{001ADD55-8617-79BD-2A75-47A3E5B17E5A}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+              <a:srcRect l="20878" t="20627" r="21613" b="4695"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545555" y="5376334"/>
+                <a:ext cx="7011395" cy="4893734"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="42" name="正方形/長方形 41">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B79B9B9-0A00-9045-F28C-B82460D4EEEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8390173" y="1813069"/>
+              <a:ext cx="1931031" cy="317135"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="43" name="直線矢印コネクタ 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D4771F-D7C6-E03C-FCDB-79D86896BAF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="10334758" y="1981050"/>
+              <a:ext cx="303446" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="44" name="正方形/長方形 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A62FAB2-43C4-8FE9-0DA3-CF8ADC3E5993}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10643475" y="1813069"/>
+              <a:ext cx="1205067" cy="317135"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>タブの切り替え</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="正方形/長方形 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B7541E9-65DA-7E77-6647-9A11D68E4038}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8414483" y="2607799"/>
+              <a:ext cx="6928932" cy="1718036"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="46" name="正方形/長方形 45">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53C52F1C-5B80-3768-5B93-4BFE087A6526}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8414483" y="5012377"/>
+              <a:ext cx="6928932" cy="6504214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="47" name="正方形/長方形 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86651245-674E-77B6-630B-BB8ED436D8A1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12777506" y="1893547"/>
+              <a:ext cx="784363" cy="435149"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>特技の例</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842D50FA-AB47-74CA-20BE-E13FAB625CAB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="47" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13173151" y="2328696"/>
+              <a:ext cx="0" cy="248249"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B3B00F-1A67-0401-9028-EB714F90A573}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="9318651" y="4665632"/>
+              <a:ext cx="291074" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="50" name="正方形/長方形 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4597EFAB-4783-9FBD-9568-5383433AB52B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9614995" y="4510669"/>
+              <a:ext cx="1472367" cy="310331"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>入力内容の読み込み</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="51" name="正方形/長方形 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D50DB2E2-CF4A-ABDB-D1EE-B2314C1A567B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8481257" y="4382047"/>
+              <a:ext cx="796538" cy="541709"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="52" name="正方形/長方形 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58480D40-DEAA-F9C8-A337-0AA37D13D857}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12863232" y="4278872"/>
+              <a:ext cx="612911" cy="435149"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>特技</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="53" name="直線矢印コネクタ 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{234AB7B2-70F0-6116-B4F5-3C02379EE7DB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="52" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="13173151" y="4714021"/>
+              <a:ext cx="1121" cy="235923"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="56" name="グループ化 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45EDE8D-B92C-435A-A09F-6112341538BC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="42318243" y="1007807"/>
+            <a:ext cx="7250380" cy="7489251"/>
+            <a:chOff x="15915569" y="1435198"/>
+            <a:chExt cx="7299541" cy="8211028"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="57" name="正方形/長方形 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E2FE23-7AE2-FACA-DBDB-415E06D236FA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15915569" y="1435198"/>
+              <a:ext cx="7299541" cy="8211028"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="58" name="グループ化 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF82CB5A-0973-AB40-A0A2-0D7DF4F046CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr>
+              <a:grpSpLocks noChangeAspect="1"/>
+            </xdr:cNvGrpSpPr>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="15965339" y="1495436"/>
+              <a:ext cx="7200000" cy="8081443"/>
+              <a:chOff x="2545554" y="-720737"/>
+              <a:chExt cx="7011398" cy="8095203"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="135" name="図 134">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F9BB571-5DB6-46E9-F465-F9451D3FCC43}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+              <a:srcRect l="20879" t="13670" r="21614"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545556" y="-720737"/>
+                <a:ext cx="7011396" cy="5657413"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="136" name="図 135">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C2FA2FE-137E-BECA-E1AD-F6946EF1EA84}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+              <a:srcRect l="20881" t="53004" r="21613" b="4876"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2545554" y="4614333"/>
+                <a:ext cx="7011398" cy="2760133"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="59" name="正方形/長方形 58">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1452C11D-E4E0-DD8C-296B-E55646DAD1C3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16010173" y="1813069"/>
+              <a:ext cx="1931030" cy="317135"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA417E72-709E-6000-904F-D2366B12E5E0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="17954757" y="1981050"/>
+              <a:ext cx="303446" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="61" name="正方形/長方形 60">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB11E37-E17B-5CA0-22FD-81E464FAAB61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="18263474" y="1813069"/>
+              <a:ext cx="1205067" cy="317135"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>タブの切り替え</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="62" name="正方形/長方形 61">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC439BB7-3353-D814-E6A9-8CBBCA4F4170}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16088911" y="2607799"/>
+              <a:ext cx="6928931" cy="4117768"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="63" name="正方形/長方形 62">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AABF4AF-B47B-2466-0BBF-4D571FBCE4D9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16088911" y="7101939"/>
+              <a:ext cx="6928931" cy="1738002"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="128" name="正方形/長方形 127">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAF1ED12-04C6-35CD-23B7-D42D21B52168}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="20934218" y="8956963"/>
+              <a:ext cx="2049607" cy="380134"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="129" name="直線矢印コネクタ 128">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7B527CE-866D-CE9B-328D-C4DCC13B1229}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="20289823" y="9158395"/>
+              <a:ext cx="618181" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="130" name="正方形/長方形 129">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C04AF138-0CC5-E550-FA62-D1487AB8B792}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="19051019" y="8997545"/>
+              <a:ext cx="1566210" cy="317136"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>データファイル出力</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="131" name="正方形/長方形 130">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2383D6EA-A2F0-25DB-FF29-D35379CCDF04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="20257180" y="1899150"/>
+              <a:ext cx="1567244" cy="435149"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>エネミーデータ確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="132" name="直線矢印コネクタ 131">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66ECEA65-57CB-0F12-1A8B-4774BE9FD4E4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="131" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="21039681" y="2334299"/>
+              <a:ext cx="1121" cy="235923"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="133" name="正方形/長方形 132">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53F7465E-B332-CCEC-2A9D-BC3EDEE2C1B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16506725" y="6427345"/>
+              <a:ext cx="1203663" cy="435149"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>CCFOLIA</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t>用出力</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="134" name="直線矢印コネクタ 133">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6405F71E-1230-7420-0E8E-C580AD3FF734}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="133" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1">
+              <a:off x="17107436" y="6862494"/>
+              <a:ext cx="1121" cy="235924"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="38100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13335,7 +16034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72C7325-9D07-4D8F-A95A-46D662A124E8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13346,7 +16045,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCF3DBF-5E6A-4390-BF66-A67313761BD1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13357,7 +16056,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F689760-5969-4AFE-B97F-3F688BB232BD}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13368,7 +16067,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E0A793-1E11-49B4-8A41-71E6489D3C17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13379,7 +16078,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC5A843-566C-4999-B9AB-70A9FADAF3B5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
